--- a/public/downloads/DickensElectronic2018.xlsx
+++ b/public/downloads/DickensElectronic2018.xlsx
@@ -8,28 +8,30 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -61,10 +63,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -161,6 +163,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -655,10 +678,10 @@
         <v>901</v>
       </c>
       <c r="N3" s="5">
-        <v>15795.58696222305</v>
+        <v>15795586.96222305</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03523960021377908</v>
+        <v>35.23960021377908</v>
       </c>
       <c r="P3" s="5">
         <v>448234</v>
@@ -705,10 +728,10 @@
         <v>901</v>
       </c>
       <c r="N4" s="5">
-        <v>11919.64776825905</v>
+        <v>11919647.76825905</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05968627609854059</v>
+        <v>59.68627609854059</v>
       </c>
       <c r="P4" s="5">
         <v>199705</v>
@@ -755,10 +778,10 @@
         <v>901</v>
       </c>
       <c r="N5" s="5">
-        <v>25933.82606172562</v>
+        <v>25933826.06172562</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1330628995619558</v>
+        <v>133.0628995619558</v>
       </c>
       <c r="P5" s="5">
         <v>194899</v>
@@ -805,10 +828,10 @@
         <v>901</v>
       </c>
       <c r="N6" s="5">
-        <v>17613.52659749985</v>
+        <v>17613526.59749985</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08591964193902364</v>
+        <v>85.91964193902365</v>
       </c>
       <c r="P6" s="5">
         <v>205000</v>
@@ -855,10 +878,10 @@
         <v>901</v>
       </c>
       <c r="N7" s="5">
-        <v>60730.74546861649</v>
+        <v>60730745.46861649</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1932254071543636</v>
+        <v>193.2254071543636</v>
       </c>
       <c r="P7" s="5">
         <v>314300</v>
@@ -905,10 +928,10 @@
         <v>901</v>
       </c>
       <c r="N8" s="5">
-        <v>5076.136497020721</v>
+        <v>5076136.497020721</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01721500370343484</v>
+        <v>17.21500370343484</v>
       </c>
       <c r="P8" s="5">
         <v>294867</v>
@@ -955,10 +978,10 @@
         <v>901</v>
       </c>
       <c r="N9" s="5">
-        <v>7029.218619823456</v>
+        <v>7029218.619823456</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03101586538510921</v>
+        <v>31.01586538510921</v>
       </c>
       <c r="P9" s="5">
         <v>226633</v>
@@ -1005,10 +1028,10 @@
         <v>901</v>
       </c>
       <c r="N10" s="5">
-        <v>21750.55796813965</v>
+        <v>21750557.96813965</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08800442627902412</v>
+        <v>88.00442627902412</v>
       </c>
       <c r="P10" s="5">
         <v>247153</v>
@@ -1055,10 +1078,10 @@
         <v>901</v>
       </c>
       <c r="N11" s="5">
-        <v>14033.18563532829</v>
+        <v>14033185.63532829</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03838892208606767</v>
+        <v>38.38892208606767</v>
       </c>
       <c r="P11" s="5">
         <v>365553</v>
@@ -1105,10 +1128,10 @@
         <v>901</v>
       </c>
       <c r="N12" s="5">
-        <v>4313.473024368286</v>
+        <v>4313473.024368286</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0203147571933024</v>
+        <v>20.31475719330241</v>
       </c>
       <c r="P12" s="5">
         <v>212332</v>
@@ -1155,10 +1178,10 @@
         <v>901</v>
       </c>
       <c r="N13" s="5">
-        <v>33510.3045694828</v>
+        <v>33510304.5694828</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07456344748672245</v>
+        <v>74.56344748672244</v>
       </c>
       <c r="P13" s="5">
         <v>449420</v>
@@ -1205,10 +1228,10 @@
         <v>901</v>
       </c>
       <c r="N14" s="5">
-        <v>62067.69851398468</v>
+        <v>62067698.51398468</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3139695504205369</v>
+        <v>313.9695504205369</v>
       </c>
       <c r="P14" s="5">
         <v>197687</v>
@@ -1255,10 +1278,10 @@
         <v>100</v>
       </c>
       <c r="N15" s="5">
-        <v>10591.85930228233</v>
+        <v>10591859.30228233</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3226176267028825</v>
+        <v>322.6176267028825</v>
       </c>
       <c r="P15" s="5">
         <v>32831</v>
@@ -1305,10 +1328,10 @@
         <v>901</v>
       </c>
       <c r="N16" s="5">
-        <v>25568.90858983994</v>
+        <v>25568908.58983994</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09993398130931976</v>
+        <v>99.93398130931976</v>
       </c>
       <c r="P16" s="5">
         <v>255858</v>
@@ -1336,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1347,9 +1370,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1383,8 +1412,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1406,132 +1443,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9077938145111697</v>
+        <v>1.65113601015179</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2251935187654651</v>
+        <v>0.3771528251030305</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3007159052827293</v>
+        <v>2.260295422271876</v>
       </c>
       <c r="E3" s="4">
-        <v>68.62739804916686</v>
+        <v>72.05305402584283</v>
       </c>
       <c r="F3" s="4">
-        <v>74.92181859072204</v>
+        <v>74.50143815915648</v>
       </c>
       <c r="G3" s="5">
         <v>378</v>
       </c>
       <c r="H3" s="5">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="I3" s="5">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J3" s="5">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K3" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L3" s="5">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.247188427441262</v>
+      </c>
+      <c r="O3" s="5">
+        <v>224</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.678050186521559</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3765058137306131</v>
+      </c>
+      <c r="R3" s="5">
+        <v>216</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5392501029461177</v>
+        <v>0.8221367375510327</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2131767351961943</v>
+        <v>0.2909789037176058</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1962164226819208</v>
+        <v>0.442635698186688</v>
       </c>
       <c r="E4" s="4">
-        <v>70.43484459652126</v>
+        <v>67.61283555338299</v>
       </c>
       <c r="F4" s="4">
-        <v>72.41289233613274</v>
+        <v>67.57200364371887</v>
       </c>
       <c r="G4" s="5">
         <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="K4" s="5">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L4" s="5">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1681567759759818</v>
+      </c>
+      <c r="O4" s="5">
+        <v>178</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7855100421988334</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2488183920391397</v>
+      </c>
+      <c r="R4" s="5">
+        <v>178</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9264428427892706</v>
+        <v>1.026724985020799</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1752890348665287</v>
+        <v>0.2425820115462407</v>
       </c>
       <c r="D5" s="4">
-        <v>0.21868790084334</v>
+        <v>1.790602987421711</v>
       </c>
       <c r="E5" s="4">
-        <v>67.07554979663816</v>
+        <v>67.97772018860444</v>
       </c>
       <c r="F5" s="4">
-        <v>74.2683735189331</v>
+        <v>72.34923002260732</v>
       </c>
       <c r="G5" s="5">
         <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I5" s="5">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J5" s="5">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K5" s="5">
         <v>8</v>
       </c>
       <c r="L5" s="5">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.06905873443462585</v>
+      </c>
+      <c r="O5" s="5">
+        <v>104</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.018201812961259</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2166314559123349</v>
+      </c>
+      <c r="R5" s="5">
+        <v>104</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1542,6 +1651,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1549,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1560,9 +1670,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1596,8 +1712,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1619,132 +1743,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>3.790662967658627</v>
+        <v>1.442203292814945</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4483826788297924</v>
+        <v>0.608118237782313</v>
       </c>
       <c r="D3" s="4">
-        <v>8.922826324938788</v>
+        <v>1.499168219334139</v>
       </c>
       <c r="E3" s="4">
-        <v>68.9625850340137</v>
+        <v>70.69457941906911</v>
       </c>
       <c r="F3" s="4">
-        <v>75.05077944675351</v>
+        <v>76.93237100955282</v>
       </c>
       <c r="G3" s="5">
         <v>378</v>
       </c>
       <c r="H3" s="5">
+        <v>224</v>
+      </c>
+      <c r="I3" s="5">
+        <v>18</v>
+      </c>
+      <c r="J3" s="5">
+        <v>136</v>
+      </c>
+      <c r="K3" s="5">
+        <v>12</v>
+      </c>
+      <c r="L3" s="5">
+        <v>96</v>
+      </c>
+      <c r="M3" s="5">
+        <v>28</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6725796954803757</v>
+      </c>
+      <c r="O3" s="5">
+        <v>252</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.441232455680298</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6126120938309888</v>
+      </c>
+      <c r="R3" s="5">
         <v>223</v>
       </c>
-      <c r="I3" s="5">
-        <v>28</v>
-      </c>
-      <c r="J3" s="5">
-        <v>127</v>
-      </c>
-      <c r="K3" s="5">
-        <v>56</v>
-      </c>
-      <c r="L3" s="5">
-        <v>67</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="S3" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>1.828686370200596</v>
+        <v>0.8222239576256808</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2540469221100163</v>
+        <v>0.5023836514445894</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7974106374042998</v>
+        <v>0.5524880483046903</v>
       </c>
       <c r="E4" s="4">
-        <v>66.85516721658729</v>
+        <v>63.56175404293452</v>
       </c>
       <c r="F4" s="4">
-        <v>68.98886790178035</v>
+        <v>65.77120925933394</v>
       </c>
       <c r="G4" s="5">
         <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="I4" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K4" s="5">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="L4" s="5">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.4534658261747487</v>
+      </c>
+      <c r="O4" s="5">
+        <v>150</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6454776109060161</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4061514809204556</v>
+      </c>
+      <c r="R4" s="5">
+        <v>150</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>2.050238137891851</v>
+        <v>1.164973004916555</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3638021074830666</v>
+        <v>0.4848033022738188</v>
       </c>
       <c r="D5" s="4">
-        <v>7.811453784014342</v>
+        <v>1.130448446096876</v>
       </c>
       <c r="E5" s="4">
-        <v>65.90307022279829</v>
+        <v>66.10517222762124</v>
       </c>
       <c r="F5" s="4">
-        <v>72.70113513961383</v>
+        <v>71.904288436727</v>
       </c>
       <c r="G5" s="5">
         <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="I5" s="5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J5" s="5">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K5" s="5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.4132577904781935</v>
+      </c>
+      <c r="O5" s="5">
+        <v>96</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.197801268785497</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4730705364731888</v>
+      </c>
+      <c r="R5" s="5">
+        <v>91</v>
+      </c>
+      <c r="S5" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1755,6 +1951,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1762,7 +1959,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1773,9 +1970,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1809,8 +2012,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1832,132 +2043,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>1.361417736902546</v>
+        <v>0.9077938145111697</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3724264443280505</v>
+        <v>0.2251935187654651</v>
       </c>
       <c r="D3" s="4">
-        <v>2.435716161294184</v>
+        <v>0.3007159052827293</v>
       </c>
       <c r="E3" s="4">
-        <v>72.2556959291655</v>
+        <v>68.62739804916686</v>
       </c>
       <c r="F3" s="4">
-        <v>75.36578364878163</v>
+        <v>74.92181859072204</v>
       </c>
       <c r="G3" s="5">
         <v>378</v>
       </c>
       <c r="H3" s="5">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="I3" s="5">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="J3" s="5">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K3" s="5">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L3" s="5">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04732556392991821</v>
+      </c>
+      <c r="O3" s="5">
+        <v>238</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8932550979070358</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2214935412288681</v>
+      </c>
+      <c r="R3" s="5">
+        <v>238</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4994864640057948</v>
+        <v>0.5392501029461177</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2381906125383095</v>
+        <v>0.2131767351961943</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3317389071566205</v>
+        <v>0.1962164226819208</v>
       </c>
       <c r="E4" s="4">
-        <v>68.97297242250193</v>
+        <v>70.43484459652126</v>
       </c>
       <c r="F4" s="4">
-        <v>70.0550911599619</v>
+        <v>72.41289233613274</v>
       </c>
       <c r="G4" s="5">
         <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K4" s="5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L4" s="5">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1541291258042835</v>
+      </c>
+      <c r="O4" s="5">
+        <v>209</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5364357581968071</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2018823953958326</v>
+      </c>
+      <c r="R4" s="5">
+        <v>209</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>1.135942672480139</v>
+        <v>0.9264428427892706</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2925926643356349</v>
+        <v>0.1752890348665287</v>
       </c>
       <c r="D5" s="4">
-        <v>2.121263282323463</v>
+        <v>0.21868790084334</v>
       </c>
       <c r="E5" s="4">
-        <v>69.78584026203066</v>
+        <v>67.07554979663816</v>
       </c>
       <c r="F5" s="4">
-        <v>73.84905839044472</v>
+        <v>74.2683735189331</v>
       </c>
       <c r="G5" s="5">
         <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="I5" s="5">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J5" s="5">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K5" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.01104473452011418</v>
+      </c>
+      <c r="O5" s="5">
+        <v>120</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9247504448617229</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1769493624843528</v>
+      </c>
+      <c r="R5" s="5">
+        <v>120</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1968,6 +2251,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1975,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1986,9 +2270,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2022,8 +2312,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2045,132 +2343,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>2.015856555513517</v>
+        <v>3.790662967658627</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3044700635414789</v>
+        <v>0.4483826788297924</v>
       </c>
       <c r="D3" s="4">
-        <v>3.846379636157171</v>
+        <v>8.922826324938788</v>
       </c>
       <c r="E3" s="4">
-        <v>70.52064211928162</v>
+        <v>68.9625850340137</v>
       </c>
       <c r="F3" s="4">
-        <v>74.53200643916473</v>
+        <v>75.05077944675351</v>
       </c>
       <c r="G3" s="5">
         <v>378</v>
       </c>
       <c r="H3" s="5">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I3" s="5">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J3" s="5">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K3" s="5">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L3" s="5">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.01224678899907383</v>
+      </c>
+      <c r="O3" s="5">
+        <v>227</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.791428640308602</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4494059537925527</v>
+      </c>
+      <c r="R3" s="5">
+        <v>223</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>1.182329522364826</v>
+        <v>1.828686370200596</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3460064864907904</v>
+        <v>0.2540469221100163</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4552550763848972</v>
+        <v>0.7974106374042998</v>
       </c>
       <c r="E4" s="4">
-        <v>67.85449509144966</v>
+        <v>66.85516721658729</v>
       </c>
       <c r="F4" s="4">
-        <v>69.4312381947515</v>
+        <v>68.98886790178035</v>
       </c>
       <c r="G4" s="5">
         <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="K4" s="5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L4" s="5">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1691039337894386</v>
+      </c>
+      <c r="O4" s="5">
+        <v>186</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.795018988828467</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2356133465817513</v>
+      </c>
+      <c r="R4" s="5">
+        <v>186</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>1.597345648951348</v>
+        <v>2.050238137891851</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2348603886925357</v>
+        <v>0.3638021074830666</v>
       </c>
       <c r="D5" s="4">
-        <v>3.486363012602153</v>
+        <v>7.811453784014342</v>
       </c>
       <c r="E5" s="4">
-        <v>68.05960479429864</v>
+        <v>65.90307022279829</v>
       </c>
       <c r="F5" s="4">
-        <v>73.59462850514262</v>
+        <v>72.70113513961383</v>
       </c>
       <c r="G5" s="5">
         <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I5" s="5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J5" s="5">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K5" s="5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L5" s="5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.02841459393161344</v>
+      </c>
+      <c r="O5" s="5">
+        <v>111</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.049614964499282</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3606360843395025</v>
+      </c>
+      <c r="R5" s="5">
+        <v>109</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2181,6 +2551,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2188,7 +2559,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2199,9 +2570,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2235,8 +2612,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2258,132 +2643,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8626534918168465</v>
+        <v>1.361417736902546</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5384251649160691</v>
+        <v>0.3724264443280505</v>
       </c>
       <c r="D3" s="4">
-        <v>0.54852917169789</v>
+        <v>2.435716161294184</v>
       </c>
       <c r="E3" s="4">
-        <v>75.47421084836044</v>
+        <v>72.2556959291655</v>
       </c>
       <c r="F3" s="4">
-        <v>79.23821952345445</v>
+        <v>75.36578364878163</v>
       </c>
       <c r="G3" s="5">
         <v>378</v>
       </c>
       <c r="H3" s="5">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="I3" s="5">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="J3" s="5">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K3" s="5">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L3" s="5">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04631419033377689</v>
+      </c>
+      <c r="O3" s="5">
+        <v>216</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.354495190163865</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3701541550202581</v>
+      </c>
+      <c r="R3" s="5">
+        <v>214</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.578555723478267</v>
+        <v>0.4994864640057948</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1614242857166875</v>
+        <v>0.2381906125383095</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1339251842165115</v>
+        <v>0.3317389071566205</v>
       </c>
       <c r="E4" s="4">
-        <v>75.18259399568218</v>
+        <v>68.97297242250193</v>
       </c>
       <c r="F4" s="4">
-        <v>75.67924553577392</v>
+        <v>70.0550911599619</v>
       </c>
       <c r="G4" s="5">
         <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="K4" s="5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L4" s="5">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1596167241311693</v>
+      </c>
+      <c r="O4" s="5">
+        <v>196</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4927999393663934</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.22917038993724</v>
+      </c>
+      <c r="R4" s="5">
+        <v>196</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4448782856910501</v>
+        <v>1.135942672480139</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2418782906528682</v>
+        <v>0.2925926643356349</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2192913823933408</v>
+        <v>2.121263282323463</v>
       </c>
       <c r="E5" s="4">
-        <v>75.82874419609102</v>
+        <v>69.78584026203066</v>
       </c>
       <c r="F5" s="4">
-        <v>80.70907756590078</v>
+        <v>73.84905839044472</v>
       </c>
       <c r="G5" s="5">
         <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="I5" s="5">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J5" s="5">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K5" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L5" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1006662352908543</v>
+      </c>
+      <c r="O5" s="5">
+        <v>107</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.13500755706841</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2996894120473066</v>
+      </c>
+      <c r="R5" s="5">
+        <v>107</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2394,6 +2851,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2401,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2412,9 +2870,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2448,8 +2912,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2471,132 +2943,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4276276371056094</v>
+        <v>2.015856555513517</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4276276371056094</v>
+        <v>0.3044700635414789</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4367145738178744</v>
+        <v>3.846379636157171</v>
       </c>
       <c r="E3" s="4">
-        <v>91.53061224489795</v>
+        <v>70.52064211928162</v>
       </c>
       <c r="F3" s="4">
-        <v>93.13758389261746</v>
+        <v>74.53200643916473</v>
       </c>
       <c r="G3" s="5">
-        <v>4</v>
+        <v>378</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05860872012056006</v>
+      </c>
+      <c r="O3" s="5">
+        <v>224</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.012875076143745</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3041318037126461</v>
+      </c>
+      <c r="R3" s="5">
+        <v>224</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.410534988693936</v>
+        <v>1.182329522364826</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2713226705212123</v>
+        <v>0.3460064864907904</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2235434018554581</v>
+        <v>0.4552550763848972</v>
       </c>
       <c r="E4" s="4">
-        <v>68.19366044290045</v>
+        <v>67.85449509144966</v>
       </c>
       <c r="F4" s="4">
-        <v>72.08006092626971</v>
+        <v>69.4312381947515</v>
       </c>
       <c r="G4" s="5">
-        <v>94</v>
+        <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="K4" s="5">
+        <v>33</v>
+      </c>
+      <c r="L4" s="5">
+        <v>110</v>
+      </c>
+      <c r="M4" s="5">
         <v>2</v>
       </c>
-      <c r="L4" s="5">
-        <v>40</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3220434922329127</v>
+      </c>
+      <c r="O4" s="5">
+        <v>186</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.071228931904146</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2354211506071273</v>
+      </c>
+      <c r="R4" s="5">
+        <v>186</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2609991305544135</v>
+        <v>1.597345648951348</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2609991305544135</v>
+        <v>0.2348603886925357</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2690911316348696</v>
+        <v>3.486363012602153</v>
       </c>
       <c r="E5" s="4">
-        <v>90.86734693877551</v>
+        <v>68.05960479429864</v>
       </c>
       <c r="F5" s="4">
-        <v>90.87248322147651</v>
+        <v>73.59462850514262</v>
       </c>
       <c r="G5" s="5">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1881830394752985</v>
+      </c>
+      <c r="O5" s="5">
+        <v>106</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.547215436163151</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1740301020442659</v>
+      </c>
+      <c r="R5" s="5">
+        <v>106</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2607,6 +3151,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2614,7 +3159,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2625,9 +3170,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2661,8 +3212,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2684,40 +3243,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9287285852437774</v>
+        <v>0.8626534918168465</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3610295387759886</v>
+        <v>0.5384251649160691</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3686886046462086</v>
+        <v>0.54852917169789</v>
       </c>
       <c r="E3" s="4">
-        <v>73.8241010689989</v>
+        <v>75.47421084836044</v>
       </c>
       <c r="F3" s="4">
-        <v>77.77245126238392</v>
+        <v>79.23821952345445</v>
       </c>
       <c r="G3" s="5">
         <v>378</v>
       </c>
       <c r="H3" s="5">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I3" s="5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" s="5">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K3" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L3" s="5">
         <v>87</v>
@@ -2725,91 +3302,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2854468493035122</v>
+      </c>
+      <c r="O3" s="5">
+        <v>245</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8065870954761147</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5359797241549215</v>
+      </c>
+      <c r="R3" s="5">
+        <v>245</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6737454757314639</v>
+        <v>0.578555723478267</v>
       </c>
       <c r="C4" s="4">
-        <v>0.153269610293429</v>
+        <v>0.1614242857166875</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1760942078250052</v>
+        <v>0.1339251842165115</v>
       </c>
       <c r="E4" s="4">
-        <v>64.36565644221763</v>
+        <v>75.18259399568218</v>
       </c>
       <c r="F4" s="4">
-        <v>63.9697115835441</v>
+        <v>75.67924553577392</v>
       </c>
       <c r="G4" s="5">
         <v>334</v>
       </c>
       <c r="H4" s="5">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="K4" s="5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L4" s="5">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1292483112624504</v>
+      </c>
+      <c r="O4" s="5">
+        <v>219</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.566614828885682</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1445445466176881</v>
+      </c>
+      <c r="R4" s="5">
+        <v>219</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6838759347880422</v>
+        <v>0.4448782856910501</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3163452252572816</v>
+        <v>0.2418782906528682</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3223081587167055</v>
+        <v>0.2192913823933408</v>
       </c>
       <c r="E5" s="4">
-        <v>73.57808731958387</v>
+        <v>75.82874419609102</v>
       </c>
       <c r="F5" s="4">
-        <v>78.08245445829345</v>
+        <v>80.70907756590078</v>
       </c>
       <c r="G5" s="5">
         <v>189</v>
       </c>
       <c r="H5" s="5">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I5" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J5" s="5">
         <v>52</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1922245836345765</v>
+      </c>
+      <c r="O5" s="5">
+        <v>125</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3923604425671373</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1352297862760636</v>
+      </c>
+      <c r="R5" s="5">
+        <v>125</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2820,12 +3451,1416 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4276276371056094</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4276276371056094</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4367145738178744</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.53061224489795</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.13758389261746</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4276276371056094</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4276276371056094</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.410534988693936</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2713226705212123</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2235434018554581</v>
+      </c>
+      <c r="E4" s="4">
+        <v>68.19366044290045</v>
+      </c>
+      <c r="F4" s="4">
+        <v>72.08006092626971</v>
+      </c>
+      <c r="G4" s="5">
+        <v>94</v>
+      </c>
+      <c r="H4" s="5">
+        <v>52</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>42</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>40</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1663805328875799</v>
+      </c>
+      <c r="O4" s="5">
+        <v>52</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3960151610245282</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2212464783141824</v>
+      </c>
+      <c r="R4" s="5">
+        <v>52</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2609991305544135</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2609991305544135</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2690911316348696</v>
+      </c>
+      <c r="E5" s="4">
+        <v>90.86734693877551</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.87248322147651</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2609991305544135</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2609991305544135</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9287285852437774</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3610295387759886</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3686886046462086</v>
+      </c>
+      <c r="E3" s="4">
+        <v>73.8241010689989</v>
+      </c>
+      <c r="F3" s="4">
+        <v>77.77245126238392</v>
+      </c>
+      <c r="G3" s="5">
+        <v>378</v>
+      </c>
+      <c r="H3" s="5">
+        <v>243</v>
+      </c>
+      <c r="I3" s="5">
+        <v>32</v>
+      </c>
+      <c r="J3" s="5">
+        <v>103</v>
+      </c>
+      <c r="K3" s="5">
+        <v>16</v>
+      </c>
+      <c r="L3" s="5">
+        <v>87</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.0143154126560397</v>
+      </c>
+      <c r="O3" s="5">
+        <v>243</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9311733841764099</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3604142220983432</v>
+      </c>
+      <c r="R3" s="5">
+        <v>243</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6737454757314639</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.153269610293429</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1760942078250052</v>
+      </c>
+      <c r="E4" s="4">
+        <v>64.36565644221763</v>
+      </c>
+      <c r="F4" s="4">
+        <v>63.9697115835441</v>
+      </c>
+      <c r="G4" s="5">
+        <v>334</v>
+      </c>
+      <c r="H4" s="5">
+        <v>169</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>164</v>
+      </c>
+      <c r="K4" s="5">
+        <v>23</v>
+      </c>
+      <c r="L4" s="5">
+        <v>138</v>
+      </c>
+      <c r="M4" s="5">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1057747015564692</v>
+      </c>
+      <c r="O4" s="5">
+        <v>172</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.680017435039984</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1748865468534773</v>
+      </c>
+      <c r="R4" s="5">
+        <v>170</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6838759347880422</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3163452252572816</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3223081587167055</v>
+      </c>
+      <c r="E5" s="4">
+        <v>73.57808731958387</v>
+      </c>
+      <c r="F5" s="4">
+        <v>78.08245445829345</v>
+      </c>
+      <c r="G5" s="5">
+        <v>189</v>
+      </c>
+      <c r="H5" s="5">
+        <v>122</v>
+      </c>
+      <c r="I5" s="5">
+        <v>15</v>
+      </c>
+      <c r="J5" s="5">
+        <v>52</v>
+      </c>
+      <c r="K5" s="5">
+        <v>6</v>
+      </c>
+      <c r="L5" s="5">
+        <v>46</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2824428683180137</v>
+      </c>
+      <c r="O5" s="5">
+        <v>122</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6566763919310379</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1947784315215254</v>
+      </c>
+      <c r="R5" s="5">
+        <v>122</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>55.38290788013318</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.216426193118757</v>
+      </c>
+      <c r="D3" s="3">
+        <v>39.40066592674805</v>
+      </c>
+      <c r="E3" s="3">
+        <v>15.53829078801332</v>
+      </c>
+      <c r="F3" s="3">
+        <v>23.75138734739179</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.1109877913429523</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.509400316861537</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2996235366622687</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.110405459649266</v>
+      </c>
+      <c r="K3" s="4">
+        <v>66.20316050948685</v>
+      </c>
+      <c r="L3" s="4">
+        <v>70.28767439608487</v>
+      </c>
+      <c r="M3" s="5">
+        <v>901</v>
+      </c>
+      <c r="N3" s="5">
+        <v>15795586.96222305</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.23960021377908</v>
+      </c>
+      <c r="P3" s="5">
+        <v>448234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>57.38068812430632</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5.105438401775805</v>
+      </c>
+      <c r="D4" s="3">
+        <v>37.51387347391787</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.440621531631521</v>
+      </c>
+      <c r="F4" s="3">
+        <v>32.0754716981132</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.997780244173141</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.6938236102994318</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4594761406760721</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.5818464516207246</v>
+      </c>
+      <c r="K4" s="4">
+        <v>67.64252870959707</v>
+      </c>
+      <c r="L4" s="4">
+        <v>73.1539030706621</v>
+      </c>
+      <c r="M4" s="5">
+        <v>901</v>
+      </c>
+      <c r="N4" s="5">
+        <v>11919647.76825905</v>
+      </c>
+      <c r="O4" s="4">
+        <v>59.68627609854059</v>
+      </c>
+      <c r="P4" s="5">
+        <v>199705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>63.04106548279689</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5.216426193118757</v>
+      </c>
+      <c r="D5" s="3">
+        <v>31.74250832408435</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4.994450610432852</v>
+      </c>
+      <c r="F5" s="3">
+        <v>24.97225305216426</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.775804661487236</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.8926452253692849</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3082279141018972</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.46024388943375</v>
+      </c>
+      <c r="K5" s="4">
+        <v>73.35451161596708</v>
+      </c>
+      <c r="L5" s="4">
+        <v>77.61172646847773</v>
+      </c>
+      <c r="M5" s="5">
+        <v>901</v>
+      </c>
+      <c r="N5" s="5">
+        <v>25933826.06172562</v>
+      </c>
+      <c r="O5" s="4">
+        <v>133.0628995619558</v>
+      </c>
+      <c r="P5" s="5">
+        <v>194899</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>57.38068812430632</v>
+      </c>
+      <c r="C6" s="3">
+        <v>6.215316315205328</v>
+      </c>
+      <c r="D6" s="3">
+        <v>36.40399556048835</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.774694783573807</v>
+      </c>
+      <c r="F6" s="3">
+        <v>30.18867924528302</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.440621531631521</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.9189158764630789</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4710060466417388</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.9121840352172327</v>
+      </c>
+      <c r="K6" s="4">
+        <v>70.90843884723708</v>
+      </c>
+      <c r="L6" s="4">
+        <v>74.31865414267551</v>
+      </c>
+      <c r="M6" s="5">
+        <v>901</v>
+      </c>
+      <c r="N6" s="5">
+        <v>17613526.59749985</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.91964193902365</v>
+      </c>
+      <c r="P6" s="5">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>59.48945615982242</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.773584905660377</v>
+      </c>
+      <c r="D7" s="3">
+        <v>36.7369589345172</v>
+      </c>
+      <c r="E7" s="3">
+        <v>9.877913429522753</v>
+      </c>
+      <c r="F7" s="3">
+        <v>26.08213096559379</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.776914539400666</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.701849600504057</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2551921924882826</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.826540293459556</v>
+      </c>
+      <c r="K7" s="4">
+        <v>71.92020204308133</v>
+      </c>
+      <c r="L7" s="4">
+        <v>75.42306956973009</v>
+      </c>
+      <c r="M7" s="5">
+        <v>901</v>
+      </c>
+      <c r="N7" s="5">
+        <v>60730745.46861649</v>
+      </c>
+      <c r="O7" s="4">
+        <v>193.2254071543636</v>
+      </c>
+      <c r="P7" s="5">
+        <v>314300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>55.27192008879024</v>
+      </c>
+      <c r="C8" s="3">
+        <v>8.213096559378469</v>
+      </c>
+      <c r="D8" s="3">
+        <v>36.5149833518313</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4.439511653718091</v>
+      </c>
+      <c r="F8" s="3">
+        <v>31.18756936736959</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.8879023307436182</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.208771883739442</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2974791184009279</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.473224606747566</v>
+      </c>
+      <c r="K8" s="4">
+        <v>69.5521982377857</v>
+      </c>
+      <c r="L8" s="4">
+        <v>71.48124008372514</v>
+      </c>
+      <c r="M8" s="5">
+        <v>901</v>
+      </c>
+      <c r="N8" s="5">
+        <v>5076136.497020721</v>
+      </c>
+      <c r="O8" s="4">
+        <v>17.21500370343484</v>
+      </c>
+      <c r="P8" s="5">
+        <v>294867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>51.49833518312985</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.883462819089901</v>
+      </c>
+      <c r="D9" s="3">
+        <v>43.61820199778024</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.995560488346282</v>
+      </c>
+      <c r="F9" s="3">
+        <v>35.84905660377358</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.773584905660377</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.095182941276605</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.5185013747444807</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.9905358156497172</v>
+      </c>
+      <c r="K9" s="4">
+        <v>67.08774075668009</v>
+      </c>
+      <c r="L9" s="4">
+        <v>71.74021159685857</v>
+      </c>
+      <c r="M9" s="5">
+        <v>901</v>
+      </c>
+      <c r="N9" s="5">
+        <v>7029218.619823456</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.01586538510921</v>
+      </c>
+      <c r="P9" s="5">
+        <v>226633</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>62.93007769145395</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5.438401775804662</v>
+      </c>
+      <c r="D10" s="3">
+        <v>31.6315205327414</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.660377358490567</v>
+      </c>
+      <c r="F10" s="3">
+        <v>25.97114317425083</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.7675891279971795</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2048374020252592</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2467340362854235</v>
+      </c>
+      <c r="K10" s="4">
+        <v>68.97189064304972</v>
+      </c>
+      <c r="L10" s="4">
+        <v>73.85469041358455</v>
+      </c>
+      <c r="M10" s="5">
+        <v>901</v>
+      </c>
+      <c r="N10" s="5">
+        <v>21750557.96813965</v>
+      </c>
+      <c r="O10" s="4">
+        <v>88.00442627902412</v>
+      </c>
+      <c r="P10" s="5">
+        <v>247153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>57.49167591564927</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.327413984461709</v>
+      </c>
+      <c r="D11" s="3">
+        <v>37.18091009988901</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12.98557158712542</v>
+      </c>
+      <c r="F11" s="3">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.6659267480577136</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2.685986233735543</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3539593501022216</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5.674981134775664</v>
+      </c>
+      <c r="K11" s="4">
+        <v>67.53958187048401</v>
+      </c>
+      <c r="L11" s="4">
+        <v>72.31075588396683</v>
+      </c>
+      <c r="M11" s="5">
+        <v>901</v>
+      </c>
+      <c r="N11" s="5">
+        <v>14033185.63532829</v>
+      </c>
+      <c r="O11" s="4">
+        <v>38.38892208606767</v>
+      </c>
+      <c r="P11" s="5">
+        <v>365553</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>57.38068812430632</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9.655937846836849</v>
+      </c>
+      <c r="D12" s="3">
+        <v>32.96337402885683</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6.659267480577137</v>
+      </c>
+      <c r="F12" s="3">
+        <v>26.08213096559379</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.2219755826859046</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.9890241841467766</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3021221522071492</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.600498760892487</v>
+      </c>
+      <c r="K12" s="4">
+        <v>70.52069884557596</v>
+      </c>
+      <c r="L12" s="4">
+        <v>73.07895527465146</v>
+      </c>
+      <c r="M12" s="5">
+        <v>901</v>
+      </c>
+      <c r="N12" s="5">
+        <v>4313473.024368286</v>
+      </c>
+      <c r="O12" s="4">
+        <v>20.31475719330241</v>
+      </c>
+      <c r="P12" s="5">
+        <v>212332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>57.26970033296337</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6.326304106548279</v>
+      </c>
+      <c r="D13" s="3">
+        <v>36.40399556048835</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10.98779134295228</v>
+      </c>
+      <c r="F13" s="3">
+        <v>25.41620421753607</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.566127590980195</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2526376915915708</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.475549346443556</v>
+      </c>
+      <c r="K13" s="4">
+        <v>69.01605925389026</v>
+      </c>
+      <c r="L13" s="4">
+        <v>72.44452472644132</v>
+      </c>
+      <c r="M13" s="5">
+        <v>901</v>
+      </c>
+      <c r="N13" s="5">
+        <v>33510304.5694828</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.56344748672244</v>
+      </c>
+      <c r="P13" s="5">
+        <v>449420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>65.37180910099889</v>
+      </c>
+      <c r="C14" s="3">
+        <v>5.327413984461709</v>
+      </c>
+      <c r="D14" s="3">
+        <v>29.3007769145394</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.773584905660377</v>
+      </c>
+      <c r="F14" s="3">
+        <v>25.52719200887902</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6307385111908748</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3053888139418292</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3030606054679599</v>
+      </c>
+      <c r="K14" s="4">
+        <v>75.4404780780237</v>
+      </c>
+      <c r="L14" s="4">
+        <v>78.2274480008535</v>
+      </c>
+      <c r="M14" s="5">
+        <v>901</v>
+      </c>
+      <c r="N14" s="5">
+        <v>62067698.51398468</v>
+      </c>
+      <c r="O14" s="4">
+        <v>313.9695504205369</v>
+      </c>
+      <c r="P14" s="5">
+        <v>197687</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>42</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.394579339458369</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2368504427908405</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2291242913735882</v>
+      </c>
+      <c r="K15" s="4">
+        <v>69.58061224489799</v>
+      </c>
+      <c r="L15" s="4">
+        <v>73.29821029082908</v>
+      </c>
+      <c r="M15" s="5">
+        <v>100</v>
+      </c>
+      <c r="N15" s="5">
+        <v>10591859.30228233</v>
+      </c>
+      <c r="O15" s="4">
+        <v>322.6176267028825</v>
+      </c>
+      <c r="P15" s="5">
+        <v>32831</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>59.37846836847947</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.327413984461709</v>
+      </c>
+      <c r="D16" s="3">
+        <v>35.29411764705883</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.994450610432852</v>
+      </c>
+      <c r="F16" s="3">
+        <v>30.07769145394007</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.2219755826859046</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.7804896787980063</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2636903506179713</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2628841685469432</v>
+      </c>
+      <c r="K16" s="4">
+        <v>70.26625744637477</v>
+      </c>
+      <c r="L16" s="4">
+        <v>72.72081480433066</v>
+      </c>
+      <c r="M16" s="5">
+        <v>901</v>
+      </c>
+      <c r="N16" s="5">
+        <v>25568908.58983994</v>
+      </c>
+      <c r="O16" s="4">
+        <v>99.93398130931976</v>
+      </c>
+      <c r="P16" s="5">
+        <v>255858</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2939,16 +4974,16 @@
         <v>52</v>
       </c>
       <c r="K3" s="5">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="M3" s="5">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>208</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -2983,16 +5018,16 @@
         <v>11</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>207</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3027,16 +5062,16 @@
         <v>12</v>
       </c>
       <c r="K5" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="M5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" s="5">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3071,16 +5106,16 @@
         <v>11</v>
       </c>
       <c r="K6" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L6" s="5">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="M6" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N6" s="5">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3115,16 +5150,16 @@
         <v>23</v>
       </c>
       <c r="K7" s="5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>289</v>
+        <v>211</v>
       </c>
       <c r="M7" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>182</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3159,16 +5194,16 @@
         <v>8</v>
       </c>
       <c r="K8" s="5">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8" s="5">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="M8" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N8" s="5">
-        <v>205</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3203,16 +5238,16 @@
         <v>16</v>
       </c>
       <c r="K9" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="M9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3247,16 +5282,16 @@
         <v>16</v>
       </c>
       <c r="K10" s="5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="M10" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N10" s="5">
-        <v>212</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3291,16 +5326,16 @@
         <v>35</v>
       </c>
       <c r="K11" s="5">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L11" s="5">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="M11" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N11" s="5">
-        <v>202</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3335,16 +5370,16 @@
         <v>16</v>
       </c>
       <c r="K12" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="M12" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>186</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3379,16 +5414,16 @@
         <v>32</v>
       </c>
       <c r="K13" s="5">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="L13" s="5">
-        <v>279</v>
+        <v>203</v>
       </c>
       <c r="M13" s="5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="N13" s="5">
-        <v>195</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3423,16 +5458,16 @@
         <v>20</v>
       </c>
       <c r="K14" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="M14" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N14" s="5">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3470,13 +5505,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M15" s="5">
         <v>2</v>
       </c>
       <c r="N15" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3511,16 +5546,16 @@
         <v>22</v>
       </c>
       <c r="K16" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="M16" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N16" s="5">
-        <v>221</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3536,9 +5571,720 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>499</v>
+      </c>
+      <c r="C3" s="5">
+        <v>47</v>
+      </c>
+      <c r="D3" s="5">
+        <v>355</v>
+      </c>
+      <c r="E3" s="5">
+        <v>140</v>
+      </c>
+      <c r="F3" s="5">
+        <v>214</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>140</v>
+      </c>
+      <c r="I3" s="5">
+        <v>111</v>
+      </c>
+      <c r="J3" s="5">
+        <v>52</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>181</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>517</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5">
+        <v>338</v>
+      </c>
+      <c r="E4" s="5">
+        <v>31</v>
+      </c>
+      <c r="F4" s="5">
+        <v>289</v>
+      </c>
+      <c r="G4" s="5">
+        <v>18</v>
+      </c>
+      <c r="H4" s="5">
+        <v>31</v>
+      </c>
+      <c r="I4" s="5">
+        <v>21</v>
+      </c>
+      <c r="J4" s="5">
+        <v>11</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>249</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>568</v>
+      </c>
+      <c r="C5" s="5">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5">
+        <v>286</v>
+      </c>
+      <c r="E5" s="5">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5">
+        <v>225</v>
+      </c>
+      <c r="G5" s="5">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5">
+        <v>45</v>
+      </c>
+      <c r="I5" s="5">
+        <v>35</v>
+      </c>
+      <c r="J5" s="5">
+        <v>12</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>205</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>517</v>
+      </c>
+      <c r="C6" s="5">
+        <v>56</v>
+      </c>
+      <c r="D6" s="5">
+        <v>328</v>
+      </c>
+      <c r="E6" s="5">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5">
+        <v>272</v>
+      </c>
+      <c r="G6" s="5">
+        <v>31</v>
+      </c>
+      <c r="H6" s="5">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5">
+        <v>21</v>
+      </c>
+      <c r="J6" s="5">
+        <v>11</v>
+      </c>
+      <c r="K6" s="5">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>242</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1</v>
+      </c>
+      <c r="N6" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>536</v>
+      </c>
+      <c r="C7" s="5">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5">
+        <v>331</v>
+      </c>
+      <c r="E7" s="5">
+        <v>89</v>
+      </c>
+      <c r="F7" s="5">
+        <v>235</v>
+      </c>
+      <c r="G7" s="5">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5">
+        <v>89</v>
+      </c>
+      <c r="I7" s="5">
+        <v>78</v>
+      </c>
+      <c r="J7" s="5">
+        <v>23</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>211</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>498</v>
+      </c>
+      <c r="C8" s="5">
+        <v>74</v>
+      </c>
+      <c r="D8" s="5">
+        <v>329</v>
+      </c>
+      <c r="E8" s="5">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5">
+        <v>281</v>
+      </c>
+      <c r="G8" s="5">
+        <v>8</v>
+      </c>
+      <c r="H8" s="5">
+        <v>40</v>
+      </c>
+      <c r="I8" s="5">
+        <v>33</v>
+      </c>
+      <c r="J8" s="5">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5">
+        <v>14</v>
+      </c>
+      <c r="L8" s="5">
+        <v>246</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>464</v>
+      </c>
+      <c r="C9" s="5">
+        <v>44</v>
+      </c>
+      <c r="D9" s="5">
+        <v>393</v>
+      </c>
+      <c r="E9" s="5">
+        <v>36</v>
+      </c>
+      <c r="F9" s="5">
+        <v>323</v>
+      </c>
+      <c r="G9" s="5">
+        <v>34</v>
+      </c>
+      <c r="H9" s="5">
+        <v>36</v>
+      </c>
+      <c r="I9" s="5">
+        <v>26</v>
+      </c>
+      <c r="J9" s="5">
+        <v>16</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>279</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>567</v>
+      </c>
+      <c r="C10" s="5">
+        <v>49</v>
+      </c>
+      <c r="D10" s="5">
+        <v>285</v>
+      </c>
+      <c r="E10" s="5">
+        <v>51</v>
+      </c>
+      <c r="F10" s="5">
+        <v>234</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>51</v>
+      </c>
+      <c r="I10" s="5">
+        <v>40</v>
+      </c>
+      <c r="J10" s="5">
+        <v>16</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>209</v>
+      </c>
+      <c r="M10" s="5">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>518</v>
+      </c>
+      <c r="C11" s="5">
+        <v>48</v>
+      </c>
+      <c r="D11" s="5">
+        <v>335</v>
+      </c>
+      <c r="E11" s="5">
+        <v>117</v>
+      </c>
+      <c r="F11" s="5">
+        <v>212</v>
+      </c>
+      <c r="G11" s="5">
+        <v>6</v>
+      </c>
+      <c r="H11" s="5">
+        <v>117</v>
+      </c>
+      <c r="I11" s="5">
+        <v>104</v>
+      </c>
+      <c r="J11" s="5">
+        <v>35</v>
+      </c>
+      <c r="K11" s="5">
+        <v>6</v>
+      </c>
+      <c r="L11" s="5">
+        <v>179</v>
+      </c>
+      <c r="M11" s="5">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>517</v>
+      </c>
+      <c r="C12" s="5">
+        <v>87</v>
+      </c>
+      <c r="D12" s="5">
+        <v>297</v>
+      </c>
+      <c r="E12" s="5">
+        <v>60</v>
+      </c>
+      <c r="F12" s="5">
+        <v>235</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5">
+        <v>60</v>
+      </c>
+      <c r="I12" s="5">
+        <v>46</v>
+      </c>
+      <c r="J12" s="5">
+        <v>16</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>217</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>516</v>
+      </c>
+      <c r="C13" s="5">
+        <v>57</v>
+      </c>
+      <c r="D13" s="5">
+        <v>328</v>
+      </c>
+      <c r="E13" s="5">
+        <v>99</v>
+      </c>
+      <c r="F13" s="5">
+        <v>229</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>99</v>
+      </c>
+      <c r="I13" s="5">
+        <v>76</v>
+      </c>
+      <c r="J13" s="5">
+        <v>32</v>
+      </c>
+      <c r="K13" s="5">
+        <v>12</v>
+      </c>
+      <c r="L13" s="5">
+        <v>203</v>
+      </c>
+      <c r="M13" s="5">
+        <v>3</v>
+      </c>
+      <c r="N13" s="5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>589</v>
+      </c>
+      <c r="C14" s="5">
+        <v>48</v>
+      </c>
+      <c r="D14" s="5">
+        <v>264</v>
+      </c>
+      <c r="E14" s="5">
+        <v>34</v>
+      </c>
+      <c r="F14" s="5">
+        <v>230</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5">
+        <v>18</v>
+      </c>
+      <c r="J14" s="5">
+        <v>20</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>204</v>
+      </c>
+      <c r="M14" s="5">
+        <v>2</v>
+      </c>
+      <c r="N14" s="5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>58</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>42</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5">
+        <v>40</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>2</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>34</v>
+      </c>
+      <c r="M15" s="5">
+        <v>2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>535</v>
+      </c>
+      <c r="C16" s="5">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5">
+        <v>318</v>
+      </c>
+      <c r="E16" s="5">
+        <v>45</v>
+      </c>
+      <c r="F16" s="5">
+        <v>271</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>45</v>
+      </c>
+      <c r="I16" s="5">
+        <v>35</v>
+      </c>
+      <c r="J16" s="5">
+        <v>22</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>243</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3549,9 +6295,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -3585,8 +6337,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3608,10 +6368,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>2.161855132710424</v>
@@ -3649,10 +6427,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.09087751357824711</v>
+      </c>
+      <c r="O3" s="5">
+        <v>211</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.162905576082264</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4023627214893686</v>
+      </c>
+      <c r="R3" s="5">
+        <v>211</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
         <v>0.9532369840999309</v>
@@ -3690,10 +6486,28 @@
       <c r="M4" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3145036901709047</v>
+      </c>
+      <c r="O4" s="5">
+        <v>181</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8527375928652385</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2408191949814025</v>
+      </c>
+      <c r="R4" s="5">
+        <v>180</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>1.367995534017388</v>
@@ -3731,9 +6545,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.07806046187966718</v>
+      </c>
+      <c r="O5" s="5">
+        <v>108</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.362841384741583</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1969088468848413</v>
+      </c>
+      <c r="R5" s="5">
+        <v>108</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3744,14 +6576,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3762,9 +6595,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -3798,8 +6637,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3821,10 +6668,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.9170330131326111</v>
@@ -3862,10 +6727,28 @@
       <c r="M3" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2987842933628546</v>
+      </c>
+      <c r="O3" s="5">
+        <v>238</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9550052183975125</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6689531326476318</v>
+      </c>
+      <c r="R3" s="5">
+        <v>224</v>
+      </c>
+      <c r="S3" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
         <v>0.5253446355086862</v>
@@ -3903,10 +6786,28 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.363614927926026</v>
+      </c>
+      <c r="O4" s="5">
+        <v>179</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.44412190953017</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2841497632279915</v>
+      </c>
+      <c r="R4" s="5">
+        <v>179</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>0.6169879202411505</v>
@@ -3944,9 +6845,27 @@
       <c r="M5" s="5">
         <v>4</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4195314504001652</v>
+      </c>
+      <c r="O5" s="5">
+        <v>118</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6127321827642943</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3231653982337654</v>
+      </c>
+      <c r="R5" s="5">
+        <v>114</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3957,14 +6876,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3975,9 +6895,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4011,8 +6937,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4034,10 +6968,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>1.154008552195024</v>
@@ -4075,10 +7027,28 @@
       <c r="M3" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1323537915290821</v>
+      </c>
+      <c r="O3" s="5">
+        <v>253</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.198920602059219</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3792381058209088</v>
+      </c>
+      <c r="R3" s="5">
+        <v>243</v>
+      </c>
+      <c r="S3" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
         <v>0.6628645194803452</v>
@@ -4116,10 +7086,28 @@
       <c r="M4" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2021321480008937</v>
+      </c>
+      <c r="O4" s="5">
+        <v>205</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6455180897847022</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2407919431262977</v>
+      </c>
+      <c r="R4" s="5">
+        <v>202</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>0.709301802162526</v>
@@ -4157,9 +7145,27 @@
       <c r="M5" s="5">
         <v>3</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.02278849075128886</v>
+      </c>
+      <c r="O5" s="5">
+        <v>126</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7168164999537059</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2786879917388994</v>
+      </c>
+      <c r="R5" s="5">
+        <v>123</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4170,14 +7176,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4188,9 +7195,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4224,8 +7237,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4247,10 +7268,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>1.082868868143883</v>
@@ -4288,10 +7327,28 @@
       <c r="M3" s="5">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5242655838065384</v>
+      </c>
+      <c r="O3" s="5">
+        <v>258</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.195554533428417</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5988148756695802</v>
+      </c>
+      <c r="R3" s="5">
+        <v>231</v>
+      </c>
+      <c r="S3" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
         <v>0.7348372342868948</v>
@@ -4329,10 +7386,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3706456977741465</v>
+      </c>
+      <c r="O4" s="5">
+        <v>181</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6530245357346726</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3371613212917616</v>
+      </c>
+      <c r="R4" s="5">
+        <v>180</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>0.7922553367881279</v>
@@ -4370,9 +7445,27 @@
       <c r="M5" s="5">
         <v>3</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.175594430949002</v>
+      </c>
+      <c r="O5" s="5">
+        <v>109</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8355206144016502</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4197627547319708</v>
+      </c>
+      <c r="R5" s="5">
+        <v>106</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4383,14 +7476,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4401,9 +7495,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4437,8 +7537,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4460,10 +7568,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>2.270835338620581</v>
@@ -4501,10 +7627,28 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1886553682821741</v>
+      </c>
+      <c r="O3" s="5">
+        <v>228</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.325630125144329</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3401149900663634</v>
+      </c>
+      <c r="R3" s="5">
+        <v>224</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
         <v>1.027657079388246</v>
@@ -4542,10 +7686,28 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2162603615566083</v>
+      </c>
+      <c r="O4" s="5">
+        <v>199</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.013839773295655</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.208682566846043</v>
+      </c>
+      <c r="R4" s="5">
+        <v>198</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>1.643869202173071</v>
@@ -4583,9 +7745,27 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1205063047459119</v>
+      </c>
+      <c r="O5" s="5">
+        <v>116</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.670136605655294</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1691062207310311</v>
+      </c>
+      <c r="R5" s="5">
+        <v>114</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4596,432 +7776,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.65113601015179</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3771528251030305</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2.260295422271876</v>
-      </c>
-      <c r="E3" s="4">
-        <v>72.05305402584283</v>
-      </c>
-      <c r="F3" s="4">
-        <v>74.50143815915648</v>
-      </c>
-      <c r="G3" s="5">
-        <v>378</v>
-      </c>
-      <c r="H3" s="5">
-        <v>217</v>
-      </c>
-      <c r="I3" s="5">
-        <v>40</v>
-      </c>
-      <c r="J3" s="5">
-        <v>121</v>
-      </c>
-      <c r="K3" s="5">
-        <v>12</v>
-      </c>
-      <c r="L3" s="5">
-        <v>102</v>
-      </c>
-      <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8221367375510327</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2909789037176058</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.442635698186688</v>
-      </c>
-      <c r="E4" s="4">
-        <v>67.61283555338299</v>
-      </c>
-      <c r="F4" s="4">
-        <v>67.57200364371887</v>
-      </c>
-      <c r="G4" s="5">
-        <v>334</v>
-      </c>
-      <c r="H4" s="5">
-        <v>178</v>
-      </c>
-      <c r="I4" s="5">
-        <v>11</v>
-      </c>
-      <c r="J4" s="5">
-        <v>145</v>
-      </c>
-      <c r="K4" s="5">
-        <v>20</v>
-      </c>
-      <c r="L4" s="5">
-        <v>125</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.026724985020799</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2425820115462407</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.790602987421711</v>
-      </c>
-      <c r="E5" s="4">
-        <v>67.97772018860444</v>
-      </c>
-      <c r="F5" s="4">
-        <v>72.34923002260732</v>
-      </c>
-      <c r="G5" s="5">
-        <v>189</v>
-      </c>
-      <c r="H5" s="5">
-        <v>104</v>
-      </c>
-      <c r="I5" s="5">
-        <v>23</v>
-      </c>
-      <c r="J5" s="5">
-        <v>62</v>
-      </c>
-      <c r="K5" s="5">
-        <v>8</v>
-      </c>
-      <c r="L5" s="5">
-        <v>54</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.442203292814945</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.608118237782313</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.499168219334139</v>
-      </c>
-      <c r="E3" s="4">
-        <v>70.69457941906911</v>
-      </c>
-      <c r="F3" s="4">
-        <v>76.93237100955282</v>
-      </c>
-      <c r="G3" s="5">
-        <v>378</v>
-      </c>
-      <c r="H3" s="5">
-        <v>224</v>
-      </c>
-      <c r="I3" s="5">
-        <v>18</v>
-      </c>
-      <c r="J3" s="5">
-        <v>136</v>
-      </c>
-      <c r="K3" s="5">
-        <v>12</v>
-      </c>
-      <c r="L3" s="5">
-        <v>96</v>
-      </c>
-      <c r="M3" s="5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8222239576256808</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5023836514445894</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5524880483046903</v>
-      </c>
-      <c r="E4" s="4">
-        <v>63.56175404293452</v>
-      </c>
-      <c r="F4" s="4">
-        <v>65.77120925933394</v>
-      </c>
-      <c r="G4" s="5">
-        <v>334</v>
-      </c>
-      <c r="H4" s="5">
-        <v>147</v>
-      </c>
-      <c r="I4" s="5">
-        <v>8</v>
-      </c>
-      <c r="J4" s="5">
-        <v>179</v>
-      </c>
-      <c r="K4" s="5">
-        <v>16</v>
-      </c>
-      <c r="L4" s="5">
-        <v>160</v>
-      </c>
-      <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.164973004916555</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4848033022738188</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.130448446096876</v>
-      </c>
-      <c r="E5" s="4">
-        <v>66.10517222762124</v>
-      </c>
-      <c r="F5" s="4">
-        <v>71.904288436727</v>
-      </c>
-      <c r="G5" s="5">
-        <v>189</v>
-      </c>
-      <c r="H5" s="5">
-        <v>90</v>
-      </c>
-      <c r="I5" s="5">
-        <v>18</v>
-      </c>
-      <c r="J5" s="5">
-        <v>81</v>
-      </c>
-      <c r="K5" s="5">
-        <v>8</v>
-      </c>
-      <c r="L5" s="5">
-        <v>67</v>
-      </c>
-      <c r="M5" s="5">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/DickensElectronic2018.xlsx
+++ b/public/downloads/DickensElectronic2018.xlsx
@@ -1503,22 +1503,22 @@
         <v>7</v>
       </c>
       <c r="N3" s="4">
-        <v>0.247188427441262</v>
+        <v>0.1306051782779321</v>
       </c>
       <c r="O3" s="5">
         <v>224</v>
       </c>
       <c r="P3" s="4">
-        <v>1.678050186521559</v>
+        <v>1.653584179197365</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3765058137306131</v>
+        <v>0.3631403071284868</v>
       </c>
       <c r="R3" s="5">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="S3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1562,16 +1562,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1681567759759818</v>
+        <v>-0.1770440105202056</v>
       </c>
       <c r="O4" s="5">
         <v>178</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7855100421988334</v>
+        <v>0.7850539203063462</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2488183920391397</v>
+        <v>0.2487309404843854</v>
       </c>
       <c r="R4" s="5">
         <v>178</v>
@@ -1621,16 +1621,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.06905873443462585</v>
+        <v>0.1213303160938466</v>
       </c>
       <c r="O5" s="5">
         <v>104</v>
       </c>
       <c r="P5" s="4">
-        <v>1.018201812961259</v>
+        <v>1.022812669024994</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2166314559123349</v>
+        <v>0.2119616717114949</v>
       </c>
       <c r="R5" s="5">
         <v>104</v>
@@ -1803,22 +1803,22 @@
         <v>28</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6725796954803757</v>
+        <v>0.4464839710199158</v>
       </c>
       <c r="O3" s="5">
         <v>252</v>
       </c>
       <c r="P3" s="4">
-        <v>1.441232455680298</v>
+        <v>1.395943385488517</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6126120938309888</v>
+        <v>0.5364844015794953</v>
       </c>
       <c r="R3" s="5">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="S3" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1862,22 +1862,22 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4534658261747487</v>
+        <v>-0.3623408005732927</v>
       </c>
       <c r="O4" s="5">
         <v>150</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6454776109060161</v>
+        <v>0.6533072894788696</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4061514809204556</v>
+        <v>0.3879308391246892</v>
       </c>
       <c r="R4" s="5">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -1921,22 +1921,22 @@
         <v>6</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4132577904781935</v>
+        <v>0.2547971109415812</v>
       </c>
       <c r="O5" s="5">
         <v>96</v>
       </c>
       <c r="P5" s="4">
-        <v>1.197801268785497</v>
+        <v>1.163196160921438</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4730705364731888</v>
+        <v>0.4337486397845674</v>
       </c>
       <c r="R5" s="5">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04732556392991821</v>
+        <v>-0.04781333282747746</v>
       </c>
       <c r="O3" s="5">
         <v>238</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8932550979070358</v>
+        <v>0.8931338008796003</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2214935412288681</v>
@@ -2162,16 +2162,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1541291258042835</v>
+        <v>-0.09161678126736206</v>
       </c>
       <c r="O4" s="5">
         <v>209</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5364357581968071</v>
+        <v>0.5279570947803526</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2018823953958326</v>
+        <v>0.193021774899314</v>
       </c>
       <c r="R4" s="5">
         <v>209</v>
@@ -2221,16 +2221,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.01104473452011418</v>
+        <v>0.03075502471478586</v>
       </c>
       <c r="O5" s="5">
         <v>120</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9247504448617229</v>
+        <v>0.932784595815575</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1769493624843528</v>
+        <v>0.1732309844672285</v>
       </c>
       <c r="R5" s="5">
         <v>120</v>
@@ -2403,16 +2403,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01224678899907383</v>
+        <v>-0.03091648753616028</v>
       </c>
       <c r="O3" s="5">
         <v>227</v>
       </c>
       <c r="P3" s="4">
-        <v>3.791428640308602</v>
+        <v>3.789598646551307</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4494059537925527</v>
+        <v>0.4471395923269422</v>
       </c>
       <c r="R3" s="5">
         <v>223</v>
@@ -2462,16 +2462,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1691039337894386</v>
+        <v>-0.1119762009766418</v>
       </c>
       <c r="O4" s="5">
         <v>186</v>
       </c>
       <c r="P4" s="4">
-        <v>1.795018988828467</v>
+        <v>1.797164584331354</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2356133465817513</v>
+        <v>0.2294095301269643</v>
       </c>
       <c r="R4" s="5">
         <v>186</v>
@@ -2521,22 +2521,22 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.02841459393161344</v>
+        <v>0.06825245950312819</v>
       </c>
       <c r="O5" s="5">
         <v>111</v>
       </c>
       <c r="P5" s="4">
-        <v>2.049614964499282</v>
+        <v>2.050335336267255</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3606360843395025</v>
+        <v>0.3737751333034711</v>
       </c>
       <c r="R5" s="5">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2703,16 +2703,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04631419033377689</v>
+        <v>-0.04122166532397387</v>
       </c>
       <c r="O3" s="5">
         <v>216</v>
       </c>
       <c r="P3" s="4">
-        <v>1.354495190163865</v>
+        <v>1.355136298363726</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3701541550202581</v>
+        <v>0.3701919248758492</v>
       </c>
       <c r="R3" s="5">
         <v>214</v>
@@ -2762,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1596167241311693</v>
+        <v>-0.08408521954515891</v>
       </c>
       <c r="O4" s="5">
         <v>196</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4927999393663934</v>
+        <v>0.4865198174618005</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.22917038993724</v>
+        <v>0.2195216681265246</v>
       </c>
       <c r="R4" s="5">
         <v>196</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1006662352908543</v>
+        <v>-0.03407984047225909</v>
       </c>
       <c r="O5" s="5">
         <v>107</v>
       </c>
       <c r="P5" s="4">
-        <v>1.13500755706841</v>
+        <v>1.133305621004655</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2996894120473066</v>
+        <v>0.2914544606400655</v>
       </c>
       <c r="R5" s="5">
         <v>107</v>
@@ -3003,16 +3003,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05860872012056006</v>
+        <v>-0.03855315895270905</v>
       </c>
       <c r="O3" s="5">
         <v>224</v>
       </c>
       <c r="P3" s="4">
-        <v>2.012875076143745</v>
+        <v>2.01283295993748</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3041318037126461</v>
+        <v>0.3026281925311553</v>
       </c>
       <c r="R3" s="5">
         <v>224</v>
@@ -3062,16 +3062,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3220434922329127</v>
+        <v>-0.2666781817097217</v>
       </c>
       <c r="O4" s="5">
         <v>186</v>
       </c>
       <c r="P4" s="4">
-        <v>1.071228931904146</v>
+        <v>1.070264791693621</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2354211506071273</v>
+        <v>0.2303214410224046</v>
       </c>
       <c r="R4" s="5">
         <v>186</v>
@@ -3121,16 +3121,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1881830394752985</v>
+        <v>-0.1708474594197469</v>
       </c>
       <c r="O5" s="5">
         <v>106</v>
       </c>
       <c r="P5" s="4">
-        <v>1.547215436163151</v>
+        <v>1.546710885100727</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1740301020442659</v>
+        <v>0.1713315026913476</v>
       </c>
       <c r="R5" s="5">
         <v>106</v>
@@ -3303,16 +3303,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2854468493035122</v>
+        <v>-0.1177928834440536</v>
       </c>
       <c r="O3" s="5">
         <v>245</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8065870954761147</v>
+        <v>0.8348963479791233</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5359797241549215</v>
+        <v>0.5327418085485</v>
       </c>
       <c r="R3" s="5">
         <v>245</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1292483112624504</v>
+        <v>-0.09009522469568809</v>
       </c>
       <c r="O4" s="5">
         <v>219</v>
       </c>
       <c r="P4" s="4">
-        <v>0.566614828885682</v>
+        <v>0.5627131178711687</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1445445466176881</v>
+        <v>0.1399566767520403</v>
       </c>
       <c r="R4" s="5">
         <v>219</v>
@@ -3421,16 +3421,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1922245836345765</v>
+        <v>0.1835144487850315</v>
       </c>
       <c r="O5" s="5">
         <v>125</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3923604425671373</v>
+        <v>0.3906969942285224</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1352297862760636</v>
+        <v>0.1343914563824405</v>
       </c>
       <c r="R5" s="5">
         <v>125</v>
@@ -3660,16 +3660,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1663805328875799</v>
+        <v>-0.2123430653082323</v>
       </c>
       <c r="O4" s="5">
         <v>52</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3960151610245282</v>
+        <v>0.4020426453118618</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2212464783141824</v>
+        <v>0.2178772601594674</v>
       </c>
       <c r="R4" s="5">
         <v>52</v>
@@ -3899,16 +3899,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0143154126560397</v>
+        <v>0.04101589822676033</v>
       </c>
       <c r="O3" s="5">
         <v>243</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9311733841764099</v>
+        <v>0.9363309649494185</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3604142220983432</v>
+        <v>0.3598120807604222</v>
       </c>
       <c r="R3" s="5">
         <v>243</v>
@@ -3958,22 +3958,22 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1057747015564692</v>
+        <v>-0.03540228433121229</v>
       </c>
       <c r="O4" s="5">
         <v>172</v>
       </c>
       <c r="P4" s="4">
-        <v>0.680017435039984</v>
+        <v>0.6715015353899489</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1748865468534773</v>
+        <v>0.1502401847448969</v>
       </c>
       <c r="R4" s="5">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -4017,16 +4017,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2824428683180137</v>
+        <v>0.2212111271510573</v>
       </c>
       <c r="O5" s="5">
         <v>122</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6566763919310379</v>
+        <v>0.6375080072377221</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1947784315215254</v>
+        <v>0.1837009273600229</v>
       </c>
       <c r="R5" s="5">
         <v>122</v>
@@ -4163,13 +4163,13 @@
         <v>0.1109877913429523</v>
       </c>
       <c r="H3" s="4">
-        <v>1.509400316861537</v>
+        <v>1.510408176666665</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2996235366622687</v>
+        <v>0.2988673602939415</v>
       </c>
       <c r="J3" s="4">
-        <v>3.110405459649266</v>
+        <v>3.108032884536997</v>
       </c>
       <c r="K3" s="4">
         <v>66.20316050948685</v>
@@ -4213,13 +4213,13 @@
         <v>1.997780244173141</v>
       </c>
       <c r="H4" s="4">
-        <v>0.6938236102994318</v>
+        <v>0.6809901977800306</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4594761406760721</v>
+        <v>0.4536214146978381</v>
       </c>
       <c r="J4" s="4">
-        <v>0.5818464516207246</v>
+        <v>0.5709976618184512</v>
       </c>
       <c r="K4" s="4">
         <v>67.64252870959707</v>
@@ -4263,13 +4263,13 @@
         <v>1.775804661487236</v>
       </c>
       <c r="H5" s="4">
-        <v>0.8926452253692849</v>
+        <v>0.8611946147053634</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3082279141018972</v>
+        <v>0.2749382541908962</v>
       </c>
       <c r="J5" s="4">
-        <v>1.46024388943375</v>
+        <v>1.441538325572571</v>
       </c>
       <c r="K5" s="4">
         <v>73.35451161596708</v>
@@ -4295,13 +4295,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>57.38068812430632</v>
+        <v>56.93673695893452</v>
       </c>
       <c r="C6" s="3">
         <v>6.215316315205328</v>
       </c>
       <c r="D6" s="3">
-        <v>36.40399556048835</v>
+        <v>36.84794672586015</v>
       </c>
       <c r="E6" s="3">
         <v>2.774694783573807</v>
@@ -4310,16 +4310,16 @@
         <v>30.18867924528302</v>
       </c>
       <c r="G6" s="3">
-        <v>3.440621531631521</v>
+        <v>3.884572697003329</v>
       </c>
       <c r="H6" s="4">
-        <v>0.9189158764630789</v>
+        <v>0.8602811443763956</v>
       </c>
       <c r="I6" s="4">
-        <v>0.4710060466417388</v>
+        <v>0.3818930623750412</v>
       </c>
       <c r="J6" s="4">
-        <v>0.9121840352172327</v>
+        <v>0.8638237364255547</v>
       </c>
       <c r="K6" s="4">
         <v>70.90843884723708</v>
@@ -4363,13 +4363,13 @@
         <v>0.776914539400666</v>
       </c>
       <c r="H7" s="4">
-        <v>1.701849600504057</v>
+        <v>1.666792572122173</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2551921924882826</v>
+        <v>0.2129257912045826</v>
       </c>
       <c r="J7" s="4">
-        <v>2.826540293459556</v>
+        <v>2.797970060009295</v>
       </c>
       <c r="K7" s="4">
         <v>71.92020204308133</v>
@@ -4395,13 +4395,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>55.27192008879024</v>
+        <v>55.38290788013318</v>
       </c>
       <c r="C8" s="3">
         <v>8.213096559378469</v>
       </c>
       <c r="D8" s="3">
-        <v>36.5149833518313</v>
+        <v>36.40399556048835</v>
       </c>
       <c r="E8" s="3">
         <v>4.439511653718091</v>
@@ -4410,16 +4410,16 @@
         <v>31.18756936736959</v>
       </c>
       <c r="G8" s="3">
-        <v>0.8879023307436182</v>
+        <v>0.776914539400666</v>
       </c>
       <c r="H8" s="4">
-        <v>1.208771883739442</v>
+        <v>1.19930568653124</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2974791184009279</v>
+        <v>0.2908207773769493</v>
       </c>
       <c r="J8" s="4">
-        <v>1.473224606747566</v>
+        <v>1.467172697465574</v>
       </c>
       <c r="K8" s="4">
         <v>69.5521982377857</v>
@@ -4445,13 +4445,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>51.49833518312985</v>
+        <v>51.05438401775805</v>
       </c>
       <c r="C9" s="3">
         <v>4.883462819089901</v>
       </c>
       <c r="D9" s="3">
-        <v>43.61820199778024</v>
+        <v>44.06215316315205</v>
       </c>
       <c r="E9" s="3">
         <v>3.995560488346282</v>
@@ -4460,16 +4460,16 @@
         <v>35.84905660377358</v>
       </c>
       <c r="G9" s="3">
-        <v>3.773584905660377</v>
+        <v>4.217536071032186</v>
       </c>
       <c r="H9" s="4">
-        <v>1.095182941276605</v>
+        <v>1.071826091914266</v>
       </c>
       <c r="I9" s="4">
-        <v>0.5185013747444807</v>
+        <v>0.4682654899114309</v>
       </c>
       <c r="J9" s="4">
-        <v>0.9905358156497172</v>
+        <v>0.9748044866284744</v>
       </c>
       <c r="K9" s="4">
         <v>67.08774075668009</v>
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.7675891279971795</v>
+        <v>0.7660805049925309</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2048374020252592</v>
+        <v>0.2007843596163927</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2467340362854235</v>
+        <v>0.2407595295164523</v>
       </c>
       <c r="K10" s="4">
         <v>68.97189064304972</v>
@@ -4545,13 +4545,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>57.49167591564927</v>
+        <v>57.60266370699223</v>
       </c>
       <c r="C11" s="3">
         <v>5.327413984461709</v>
       </c>
       <c r="D11" s="3">
-        <v>37.18091009988901</v>
+        <v>37.06992230854606</v>
       </c>
       <c r="E11" s="3">
         <v>12.98557158712542</v>
@@ -4560,16 +4560,16 @@
         <v>23.52941176470588</v>
       </c>
       <c r="G11" s="3">
-        <v>0.6659267480577136</v>
+        <v>0.5549389567147613</v>
       </c>
       <c r="H11" s="4">
-        <v>2.685986233735543</v>
+        <v>2.686164970163793</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3539593501022216</v>
+        <v>0.3535598581038638</v>
       </c>
       <c r="J11" s="4">
-        <v>5.674981134775664</v>
+        <v>5.672420075656174</v>
       </c>
       <c r="K11" s="4">
         <v>67.53958187048401</v>
@@ -4613,13 +4613,13 @@
         <v>0.2219755826859046</v>
       </c>
       <c r="H12" s="4">
-        <v>0.9890241841467766</v>
+        <v>0.986608104532308</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3021221522071492</v>
+        <v>0.2967755244965524</v>
       </c>
       <c r="J12" s="4">
-        <v>1.600498760892487</v>
+        <v>1.589711832167727</v>
       </c>
       <c r="K12" s="4">
         <v>70.52069884557596</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>1.566127590980195</v>
+        <v>1.5656466776538</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2526376915915708</v>
+        <v>0.2495923303147847</v>
       </c>
       <c r="J13" s="4">
-        <v>2.475549346443556</v>
+        <v>2.470518307238471</v>
       </c>
       <c r="K13" s="4">
         <v>69.01605925389026</v>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.6307385111908748</v>
+        <v>0.6408199032344835</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3053888139418292</v>
+        <v>0.3021582128198376</v>
       </c>
       <c r="J14" s="4">
-        <v>0.3030606054679599</v>
+        <v>0.2986366613618973</v>
       </c>
       <c r="K14" s="4">
         <v>75.4404780780237</v>
@@ -4763,13 +4763,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.394579339458369</v>
+        <v>0.4002451746884627</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2368504427908405</v>
+        <v>0.2338297644452339</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2291242913735882</v>
+        <v>0.2404907436019807</v>
       </c>
       <c r="K15" s="4">
         <v>69.58061224489799</v>
@@ -4795,13 +4795,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3">
-        <v>59.37846836847947</v>
+        <v>59.26748057713651</v>
       </c>
       <c r="C16" s="3">
         <v>5.327413984461709</v>
       </c>
       <c r="D16" s="3">
-        <v>35.29411764705883</v>
+        <v>35.40510543840178</v>
       </c>
       <c r="E16" s="3">
         <v>4.994450610432852</v>
@@ -4810,16 +4810,16 @@
         <v>30.07769145394007</v>
       </c>
       <c r="G16" s="3">
-        <v>0.2219755826859046</v>
+        <v>0.3329633740288568</v>
       </c>
       <c r="H16" s="4">
-        <v>0.7804896787980063</v>
+        <v>0.7754757280122671</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2636903506179713</v>
+        <v>0.2532517602707733</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2628841685469432</v>
+        <v>0.2560877356841862</v>
       </c>
       <c r="K16" s="4">
         <v>70.26625744637477</v>
@@ -5790,13 +5790,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C6" s="5">
         <v>56</v>
       </c>
       <c r="D6" s="5">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E6" s="5">
         <v>25</v>
@@ -5805,7 +5805,7 @@
         <v>272</v>
       </c>
       <c r="G6" s="5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5">
         <v>25</v>
@@ -5878,13 +5878,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C8" s="5">
         <v>74</v>
       </c>
       <c r="D8" s="5">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
@@ -5893,7 +5893,7 @@
         <v>281</v>
       </c>
       <c r="G8" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" s="5">
         <v>40</v>
@@ -5922,13 +5922,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C9" s="5">
         <v>44</v>
       </c>
       <c r="D9" s="5">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E9" s="5">
         <v>36</v>
@@ -5937,7 +5937,7 @@
         <v>323</v>
       </c>
       <c r="G9" s="5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H9" s="5">
         <v>36</v>
@@ -6010,13 +6010,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C11" s="5">
         <v>48</v>
       </c>
       <c r="D11" s="5">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E11" s="5">
         <v>117</v>
@@ -6025,7 +6025,7 @@
         <v>212</v>
       </c>
       <c r="G11" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" s="5">
         <v>117</v>
@@ -6230,13 +6230,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="5">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C16" s="5">
         <v>48</v>
       </c>
       <c r="D16" s="5">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E16" s="5">
         <v>45</v>
@@ -6245,7 +6245,7 @@
         <v>271</v>
       </c>
       <c r="G16" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="5">
         <v>45</v>
@@ -6428,16 +6428,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.09087751357824711</v>
+        <v>0.1176997435759404</v>
       </c>
       <c r="O3" s="5">
         <v>211</v>
       </c>
       <c r="P3" s="4">
-        <v>2.162905576082264</v>
+        <v>2.164519462040579</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4023627214893686</v>
+        <v>0.4019335680436059</v>
       </c>
       <c r="R3" s="5">
         <v>211</v>
@@ -6487,16 +6487,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3145036901709047</v>
+        <v>-0.2893332688399823</v>
       </c>
       <c r="O4" s="5">
         <v>181</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8527375928652385</v>
+        <v>0.8532882702766836</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2408191949814025</v>
+        <v>0.2393596142723254</v>
       </c>
       <c r="R4" s="5">
         <v>180</v>
@@ -6546,16 +6546,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.07806046187966718</v>
+        <v>0.09062070186701021</v>
       </c>
       <c r="O5" s="5">
         <v>108</v>
       </c>
       <c r="P5" s="4">
-        <v>1.362841384741583</v>
+        <v>1.363445123031294</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1969088468848413</v>
+        <v>0.19668610518942</v>
       </c>
       <c r="R5" s="5">
         <v>108</v>
@@ -6728,16 +6728,16 @@
         <v>14</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2987842933628546</v>
+        <v>0.2436368804119411</v>
       </c>
       <c r="O3" s="5">
         <v>238</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9550052183975125</v>
+        <v>0.9438527628908512</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6689531326476318</v>
+        <v>0.6654795478024847</v>
       </c>
       <c r="R3" s="5">
         <v>224</v>
@@ -6787,16 +6787,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.363614927926026</v>
+        <v>-0.3146483529708348</v>
       </c>
       <c r="O4" s="5">
         <v>179</v>
       </c>
       <c r="P4" s="4">
-        <v>0.44412190953017</v>
+        <v>0.4389849542266549</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2841497632279915</v>
+        <v>0.2794975883562938</v>
       </c>
       <c r="R4" s="5">
         <v>179</v>
@@ -6846,16 +6846,16 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4195314504001652</v>
+        <v>0.3151614127273206</v>
       </c>
       <c r="O5" s="5">
         <v>118</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6127321827642943</v>
+        <v>0.5829357096050954</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3231653982337654</v>
+        <v>0.3107437225899048</v>
       </c>
       <c r="R5" s="5">
         <v>114</v>
@@ -7028,16 +7028,16 @@
         <v>10</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1323537915290821</v>
+        <v>-0.07489369566610549</v>
       </c>
       <c r="O3" s="5">
         <v>253</v>
       </c>
       <c r="P3" s="4">
-        <v>1.198920602059219</v>
+        <v>1.14011793833935</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3792381058209088</v>
+        <v>0.323136723280081</v>
       </c>
       <c r="R3" s="5">
         <v>243</v>
@@ -7087,16 +7087,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2021321480008937</v>
+        <v>-0.09394987490668427</v>
       </c>
       <c r="O4" s="5">
         <v>205</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6455180897847022</v>
+        <v>0.6397768241917938</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2407919431262977</v>
+        <v>0.2212846890100505</v>
       </c>
       <c r="R4" s="5">
         <v>202</v>
@@ -7146,16 +7146,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>0.02278849075128886</v>
+        <v>-0.06366762494144496</v>
       </c>
       <c r="O5" s="5">
         <v>126</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7168164999537059</v>
+        <v>0.6946365496148087</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2786879917388994</v>
+        <v>0.2678308735230826</v>
       </c>
       <c r="R5" s="5">
         <v>123</v>
@@ -7328,22 +7328,22 @@
         <v>30</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5242655838065384</v>
+        <v>0.1534592629250255</v>
       </c>
       <c r="O3" s="5">
         <v>258</v>
       </c>
       <c r="P3" s="4">
-        <v>1.195554533428417</v>
+        <v>1.082405145289485</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5988148756695802</v>
+        <v>0.4332852113187057</v>
       </c>
       <c r="R3" s="5">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="S3" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7387,22 +7387,22 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3706456977741465</v>
+        <v>-0.2675607649507583</v>
       </c>
       <c r="O4" s="5">
         <v>181</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6530245357346726</v>
+        <v>0.644874592633696</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3371613212917616</v>
+        <v>0.3080691677008791</v>
       </c>
       <c r="R4" s="5">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7446,16 +7446,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>0.175594430949002</v>
+        <v>0.03240247834764887</v>
       </c>
       <c r="O5" s="5">
         <v>109</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8355206144016502</v>
+        <v>0.796698689016151</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4197627547319708</v>
+        <v>0.396016337728999</v>
       </c>
       <c r="R5" s="5">
         <v>106</v>
@@ -7628,16 +7628,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1886553682821741</v>
+        <v>-0.02309638200313202</v>
       </c>
       <c r="O3" s="5">
         <v>228</v>
       </c>
       <c r="P3" s="4">
-        <v>2.325630125144329</v>
+        <v>2.267844225978431</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3401149900663634</v>
+        <v>0.2759897631619067</v>
       </c>
       <c r="R3" s="5">
         <v>224</v>
@@ -7687,16 +7687,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2162603615566083</v>
+        <v>-0.1279597924876725</v>
       </c>
       <c r="O4" s="5">
         <v>199</v>
       </c>
       <c r="P4" s="4">
-        <v>1.013839773295655</v>
+        <v>0.9991072119208151</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.208682566846043</v>
+        <v>0.1845107031725028</v>
       </c>
       <c r="R4" s="5">
         <v>198</v>
@@ -7746,16 +7746,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1205063047459119</v>
+        <v>0.01752758033399004</v>
       </c>
       <c r="O5" s="5">
         <v>116</v>
       </c>
       <c r="P5" s="4">
-        <v>1.670136605655294</v>
+        <v>1.64462000677608</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1691062207310311</v>
+        <v>0.1383631395546808</v>
       </c>
       <c r="R5" s="5">
         <v>114</v>
